--- a/Electronics/PCBs/Analog Reader/PickAndPlace.xlsx
+++ b/Electronics/PCBs/Analog Reader/PickAndPlace.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="117">
   <si>
     <t>Designator</t>
   </si>
@@ -161,6 +161,207 @@
   </si>
   <si>
     <t>-21mm</t>
+  </si>
+  <si>
+    <t>B7B-PH</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>CL10A105KB8NNNC</t>
+  </si>
+  <si>
+    <t>C0603</t>
+  </si>
+  <si>
+    <t>28mm</t>
+  </si>
+  <si>
+    <t>-6.5mm</t>
+  </si>
+  <si>
+    <t>-7.2mm</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>30mm</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>32mm</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>34mm</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>10.028mm</t>
+  </si>
+  <si>
+    <t>-11.472mm</t>
+  </si>
+  <si>
+    <t>-12.172mm</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>8.028mm</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>6.028mm</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>-11.5mm</t>
+  </si>
+  <si>
+    <t>-12.2mm</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>4.028mm</t>
+  </si>
+  <si>
+    <t>-18.528mm</t>
+  </si>
+  <si>
+    <t>-19.228mm</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>-23.5mm</t>
+  </si>
+  <si>
+    <t>-24.2mm</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>0603WAF4701T5E</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>-3.5mm</t>
+  </si>
+  <si>
+    <t>-2.747mm</t>
+  </si>
+  <si>
+    <t>4.7kΩ</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>-8.472mm</t>
+  </si>
+  <si>
+    <t>-7.719mm</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>-8.5mm</t>
+  </si>
+  <si>
+    <t>-7.747mm</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>-21.528mm</t>
+  </si>
+  <si>
+    <t>-20.774mm</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>-26.5mm</t>
+  </si>
+  <si>
+    <t>-25.747mm</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>R16</t>
   </si>
 </sst>
 </file>
@@ -537,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -892,7 +1093,1415 @@
         <v>35</v>
       </c>
       <c r="N8" t="s">
-        <v>46</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9">
+        <v>90</v>
+      </c>
+      <c r="M9" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10">
+        <v>90</v>
+      </c>
+      <c r="M10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11">
+        <v>90</v>
+      </c>
+      <c r="M11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" t="s">
+        <v>56</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12">
+        <v>90</v>
+      </c>
+      <c r="M12" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13">
+        <v>90</v>
+      </c>
+      <c r="M13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14">
+        <v>90</v>
+      </c>
+      <c r="M14" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15">
+        <v>90</v>
+      </c>
+      <c r="M15" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16">
+        <v>90</v>
+      </c>
+      <c r="M16" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17">
+        <v>90</v>
+      </c>
+      <c r="M17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" t="s">
+        <v>71</v>
+      </c>
+      <c r="I18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18">
+        <v>90</v>
+      </c>
+      <c r="M18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" t="s">
+        <v>78</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19">
+        <v>90</v>
+      </c>
+      <c r="M19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20" t="s">
+        <v>78</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20">
+        <v>90</v>
+      </c>
+      <c r="M20" t="s">
+        <v>22</v>
+      </c>
+      <c r="N20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" t="s">
+        <v>84</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21">
+        <v>90</v>
+      </c>
+      <c r="M21" t="s">
+        <v>22</v>
+      </c>
+      <c r="N21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" t="s">
+        <v>84</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22">
+        <v>90</v>
+      </c>
+      <c r="M22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I23" t="s">
+        <v>84</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23">
+        <v>90</v>
+      </c>
+      <c r="M23" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" t="s">
+        <v>54</v>
+      </c>
+      <c r="I24" t="s">
+        <v>84</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24">
+        <v>90</v>
+      </c>
+      <c r="M24" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" t="s">
+        <v>54</v>
+      </c>
+      <c r="I25" t="s">
+        <v>92</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25">
+        <v>270</v>
+      </c>
+      <c r="M25" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" t="s">
+        <v>59</v>
+      </c>
+      <c r="I26" t="s">
+        <v>92</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26">
+        <v>270</v>
+      </c>
+      <c r="M26" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I27" t="s">
+        <v>92</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27">
+        <v>270</v>
+      </c>
+      <c r="M27" t="s">
+        <v>22</v>
+      </c>
+      <c r="N27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" t="s">
+        <v>63</v>
+      </c>
+      <c r="G28" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" t="s">
+        <v>63</v>
+      </c>
+      <c r="I28" t="s">
+        <v>92</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28">
+        <v>270</v>
+      </c>
+      <c r="M28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29" t="s">
+        <v>98</v>
+      </c>
+      <c r="H29" t="s">
+        <v>65</v>
+      </c>
+      <c r="I29" t="s">
+        <v>99</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29">
+        <v>270</v>
+      </c>
+      <c r="M29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N29" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" t="s">
+        <v>98</v>
+      </c>
+      <c r="H30" t="s">
+        <v>69</v>
+      </c>
+      <c r="I30" t="s">
+        <v>99</v>
+      </c>
+      <c r="J30">
+        <v>2</v>
+      </c>
+      <c r="K30" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30">
+        <v>270</v>
+      </c>
+      <c r="M30" t="s">
+        <v>22</v>
+      </c>
+      <c r="N30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" t="s">
+        <v>98</v>
+      </c>
+      <c r="H31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I31" t="s">
+        <v>99</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31">
+        <v>270</v>
+      </c>
+      <c r="M31" t="s">
+        <v>22</v>
+      </c>
+      <c r="N31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" t="s">
+        <v>103</v>
+      </c>
+      <c r="H32" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" t="s">
+        <v>104</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32">
+        <v>270</v>
+      </c>
+      <c r="M32" t="s">
+        <v>22</v>
+      </c>
+      <c r="N32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" t="s">
+        <v>106</v>
+      </c>
+      <c r="F33" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" t="s">
+        <v>106</v>
+      </c>
+      <c r="H33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" t="s">
+        <v>107</v>
+      </c>
+      <c r="J33">
+        <v>2</v>
+      </c>
+      <c r="K33" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33">
+        <v>270</v>
+      </c>
+      <c r="M33" t="s">
+        <v>22</v>
+      </c>
+      <c r="N33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G34" t="s">
+        <v>106</v>
+      </c>
+      <c r="H34" t="s">
+        <v>71</v>
+      </c>
+      <c r="I34" t="s">
+        <v>107</v>
+      </c>
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="K34" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34">
+        <v>270</v>
+      </c>
+      <c r="M34" t="s">
+        <v>22</v>
+      </c>
+      <c r="N34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" t="s">
+        <v>69</v>
+      </c>
+      <c r="G35" t="s">
+        <v>106</v>
+      </c>
+      <c r="H35" t="s">
+        <v>69</v>
+      </c>
+      <c r="I35" t="s">
+        <v>107</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35">
+        <v>270</v>
+      </c>
+      <c r="M35" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" t="s">
+        <v>65</v>
+      </c>
+      <c r="G36" t="s">
+        <v>106</v>
+      </c>
+      <c r="H36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I36" t="s">
+        <v>107</v>
+      </c>
+      <c r="J36">
+        <v>2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36">
+        <v>270</v>
+      </c>
+      <c r="M36" t="s">
+        <v>22</v>
+      </c>
+      <c r="N36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" t="s">
+        <v>112</v>
+      </c>
+      <c r="F37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G37" t="s">
+        <v>112</v>
+      </c>
+      <c r="H37" t="s">
+        <v>63</v>
+      </c>
+      <c r="I37" t="s">
+        <v>113</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37">
+        <v>270</v>
+      </c>
+      <c r="M37" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" t="s">
+        <v>112</v>
+      </c>
+      <c r="F38" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" t="s">
+        <v>112</v>
+      </c>
+      <c r="H38" t="s">
+        <v>61</v>
+      </c>
+      <c r="I38" t="s">
+        <v>113</v>
+      </c>
+      <c r="J38">
+        <v>2</v>
+      </c>
+      <c r="K38" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38">
+        <v>270</v>
+      </c>
+      <c r="M38" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" t="s">
+        <v>112</v>
+      </c>
+      <c r="F39" t="s">
+        <v>59</v>
+      </c>
+      <c r="G39" t="s">
+        <v>112</v>
+      </c>
+      <c r="H39" t="s">
+        <v>59</v>
+      </c>
+      <c r="I39" t="s">
+        <v>113</v>
+      </c>
+      <c r="J39">
+        <v>2</v>
+      </c>
+      <c r="K39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39">
+        <v>270</v>
+      </c>
+      <c r="M39" t="s">
+        <v>22</v>
+      </c>
+      <c r="N39" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" t="s">
+        <v>112</v>
+      </c>
+      <c r="F40" t="s">
+        <v>54</v>
+      </c>
+      <c r="G40" t="s">
+        <v>112</v>
+      </c>
+      <c r="H40" t="s">
+        <v>54</v>
+      </c>
+      <c r="I40" t="s">
+        <v>113</v>
+      </c>
+      <c r="J40">
+        <v>2</v>
+      </c>
+      <c r="K40" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40">
+        <v>270</v>
+      </c>
+      <c r="M40" t="s">
+        <v>22</v>
+      </c>
+      <c r="N40" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
